--- a/sheets/대금율보/검수/시나위.xlsx
+++ b/sheets/대금율보/검수/시나위.xlsx
@@ -14035,7 +14035,7 @@
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林?
+          <t xml:space="preserve">林
 林
 –</t>
         </is>
@@ -14043,7 +14043,7 @@
       <c r="C3" s="22"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南?
+          <t xml:space="preserve">南
 –)
 南)</t>
         </is>
@@ -14313,7 +14313,7 @@
       <c r="I9" s="26"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林?
+          <t xml:space="preserve">林
 林
 –</t>
         </is>
@@ -14330,7 +14330,7 @@
       <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-林?
+林
 林</t>
         </is>
       </c>
@@ -14437,7 +14437,7 @@
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林?
+          <t xml:space="preserve">林
 南)
 –</t>
         </is>
@@ -14490,7 +14490,7 @@
       <c r="K12" s="24"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林?
+          <t xml:space="preserve">林
 太
 –</t>
         </is>
@@ -14573,7 +14573,7 @@
       <c r="G15" s="26"/>
       <c r="H15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林?
+          <t xml:space="preserve">林
 林
 –太</t>
         </is>
@@ -14589,7 +14589,7 @@
       <c r="K15" s="24"/>
       <c r="L15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林?
+          <t xml:space="preserve">林
 林
 –</t>
         </is>
@@ -14614,14 +14614,14 @@
       <c r="R15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-南?
+南
 南)</t>
         </is>
       </c>
       <c r="S15" s="22"/>
       <c r="T15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林?
+          <t xml:space="preserve">林
 林
 –</t>
         </is>
@@ -14648,7 +14648,7 @@
       <c r="G16" s="24"/>
       <c r="H16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林?
+          <t xml:space="preserve">林
 南)
 –</t>
         </is>
@@ -14657,7 +14657,7 @@
       <c r="J16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-南?</t>
+南</t>
         </is>
       </c>
       <c r="K16" s="22"/>
@@ -14694,7 +14694,7 @@
       <c r="G17" s="24"/>
       <c r="H17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林?
+          <t xml:space="preserve">林
 太
 –</t>
         </is>
@@ -14832,7 +14832,7 @@
       <c r="C21" s="24"/>
       <c r="D21" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰?</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="E21" s="22"/>
@@ -15110,7 +15110,7 @@
       <c r="G27" s="24"/>
       <c r="H27" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林?
+          <t xml:space="preserve">林
 林
 –南</t>
         </is>
@@ -15140,7 +15140,7 @@
       <c r="O27" s="24"/>
       <c r="P27" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林仲?
+          <t xml:space="preserve">林仲
 林
 –汰</t>
         </is>
@@ -15156,7 +15156,7 @@
       <c r="S27" s="24"/>
       <c r="T27" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林?
+          <t xml:space="preserve">林
 林
 –</t>
         </is>
@@ -15252,7 +15252,7 @@
       <c r="C29" s="24"/>
       <c r="D29" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰?
+          <t xml:space="preserve">汰
 淋
 –</t>
         </is>
@@ -15260,7 +15260,7 @@
       <c r="E29" s="22"/>
       <c r="F29" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋?
+          <t xml:space="preserve">淋
 淋
 –</t>
         </is>
@@ -15268,7 +15268,7 @@
       <c r="G29" s="22"/>
       <c r="H29" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林?
+          <t xml:space="preserve">林
 太
 –</t>
         </is>
@@ -15285,7 +15285,7 @@
       <c r="L29" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-林?
+林
 太</t>
         </is>
       </c>
@@ -15335,7 +15335,7 @@
       <c r="E30" s="24"/>
       <c r="F30" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋?
+          <t xml:space="preserve">淋
 –
 △</t>
         </is>
@@ -15424,7 +15424,7 @@
       <c r="A33" s="0"/>
       <c r="B33" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋?</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="C33" s="22"/>
@@ -15476,7 +15476,7 @@
       <c r="O33" s="24"/>
       <c r="P33" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林?
+          <t xml:space="preserve">林
 林
 –</t>
         </is>
@@ -15659,7 +15659,7 @@
       <c r="T35" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潕潕ㄷ
-△淋?
+△淋
 淋</t>
         </is>
       </c>
@@ -15814,7 +15814,7 @@
         <is>
           <t xml:space="preserve">湳
 –)
-㳞?</t>
+㳞</t>
         </is>
       </c>
       <c r="M39" s="22"/>
@@ -15865,7 +15865,7 @@
       <c r="G40" s="24"/>
       <c r="H40" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋?
+          <t xml:space="preserve">淋
 淋
 –</t>
         </is>
@@ -15873,7 +15873,7 @@
       <c r="I40" s="22"/>
       <c r="J40" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋?
+          <t xml:space="preserve">淋
 淋
 –</t>
         </is>
@@ -15881,7 +15881,7 @@
       <c r="K40" s="22"/>
       <c r="L40" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋?
+          <t xml:space="preserve">淋
 淋
 –</t>
         </is>
@@ -15954,7 +15954,7 @@
         <is>
           <t xml:space="preserve">潕ㄷ
 湳)
-㳞?</t>
+㳞</t>
         </is>
       </c>
       <c r="M41" s="22"/>
@@ -15976,7 +15976,7 @@
       <c r="Q41" s="24"/>
       <c r="R41" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林?
+          <t xml:space="preserve">林
 林
 –
 ㄴ</t>
@@ -15985,7 +15985,7 @@
       <c r="S41" s="22"/>
       <c r="T41" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋?
+          <t xml:space="preserve">淋
 淋
 –㳞</t>
         </is>
@@ -16020,7 +16020,7 @@
       <c r="G42" s="24"/>
       <c r="H42" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋?
+          <t xml:space="preserve">淋
 淋
 –</t>
         </is>
@@ -16028,7 +16028,7 @@
       <c r="I42" s="22"/>
       <c r="J42" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋?
+          <t xml:space="preserve">淋
 淋
 –</t>
         </is>
@@ -16036,7 +16036,7 @@
       <c r="K42" s="22"/>
       <c r="L42" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋?
+          <t xml:space="preserve">淋
 淋
 –</t>
         </is>
@@ -16160,7 +16160,7 @@
       <c r="R45" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰淋
-㳞?
+㳞
 㳞</t>
         </is>
       </c>
@@ -16181,7 +16181,7 @@
       <c r="D46" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-湳?
+湳
 湳</t>
         </is>
       </c>
@@ -16238,7 +16238,7 @@
       <c r="S46" s="24"/>
       <c r="T46" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋?</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="U46" s="22"/>
@@ -16413,7 +16413,7 @@
       <c r="A51" s="0"/>
       <c r="B51" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㑣?
+          <t xml:space="preserve">㑣
 㑣
 –</t>
         </is>
@@ -16429,13 +16429,13 @@
       <c r="E51" s="24"/>
       <c r="F51" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㑲?</t>
+          <t xml:space="preserve">㑲</t>
         </is>
       </c>
       <c r="G51" s="22"/>
       <c r="H51" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰?</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="I51" s="22"/>
@@ -16471,7 +16471,7 @@
       <c r="Q51" s="24"/>
       <c r="R51" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋?
+          <t xml:space="preserve">淋
 淋
 –</t>
         </is>
@@ -16505,8 +16505,8 @@
       <c r="J52" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞∧
-㳞?
-㳞?</t>
+㳞
+㳞</t>
         </is>
       </c>
       <c r="K52" s="22"/>
@@ -16588,7 +16588,7 @@
       <c r="G54" s="24"/>
       <c r="H54" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南?</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I54" s="22"/>
@@ -16729,7 +16729,7 @@
         <is>
           <t xml:space="preserve">南)
 –
-林?</t>
+林</t>
         </is>
       </c>
       <c r="Q57" s="22"/>
@@ -17026,7 +17026,7 @@
       <c r="I63" s="24"/>
       <c r="J63" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞淋?
+          <t xml:space="preserve">㳞淋
 㳞淋
 㳞淋</t>
         </is>
@@ -17035,7 +17035,7 @@
       <c r="L63" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潕潕ㄷ
-㳞淋?
+㳞淋
 㳞</t>
         </is>
       </c>
@@ -17083,7 +17083,7 @@
       <c r="I64" s="24"/>
       <c r="J64" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞淋?
+          <t xml:space="preserve">㳞淋
 㳞淋
 㳞淋</t>
         </is>
@@ -17151,7 +17151,7 @@
       <c r="L65" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-△淋?
+△淋
 㳞</t>
         </is>
       </c>
@@ -17166,7 +17166,7 @@
       <c r="O65" s="24"/>
       <c r="P65" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋?
+          <t xml:space="preserve">淋
 淋
 –</t>
         </is>
@@ -17327,7 +17327,7 @@
       <c r="J69" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰淋
-㳞?
+㳞
 㳞</t>
         </is>
       </c>
@@ -17358,7 +17358,7 @@
       <c r="Q69" s="24"/>
       <c r="R69" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林?
+          <t xml:space="preserve">林
 林
 –</t>
         </is>
@@ -17386,7 +17386,7 @@
       <c r="D70" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–㳞
-汰?
+汰
 㳞</t>
         </is>
       </c>

--- a/sheets/대금율보/검수/시나위.xlsx
+++ b/sheets/대금율보/검수/시나위.xlsx
@@ -13979,32 +13979,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="15.29" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="15.29" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="15.29" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="15.29" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="15.29" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="102.56" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="458.98" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
       </c>
       <c r="U3" s="26"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="458.98" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="23"/>
       <c r="C4" s="24"/>
@@ -14149,7 +14149,7 @@
       <c r="T4" s="23"/>
       <c r="U4" s="24"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="458.98" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="23"/>
       <c r="C5" s="24"/>
@@ -14178,7 +14178,7 @@
       <c r="T5" s="23"/>
       <c r="U5" s="24"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="458.98" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -14249,10 +14249,10 @@
       </c>
       <c r="U6" s="24"/>
     </row>
-    <row r="7">
+    <row r="7" ht="6.0" customHeight="true">
       <c r="A7" s="0"/>
     </row>
-    <row r="8" ht="60" customHeight="1">
+    <row r="8" ht="102.56" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="20" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
       <c r="T8" s="20"/>
       <c r="U8" s="20"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="458.98" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
       </c>
       <c r="U9" s="24"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="458.98" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="23"/>
       <c r="C10" s="24"/>
@@ -14411,7 +14411,7 @@
       <c r="T10" s="23"/>
       <c r="U10" s="24"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="458.98" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="23"/>
       <c r="C11" s="24"/>
@@ -14458,7 +14458,7 @@
       <c r="T11" s="23"/>
       <c r="U11" s="24"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="458.98" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="23" t="inlineStr">
         <is>
@@ -14517,10 +14517,10 @@
       <c r="T12" s="23"/>
       <c r="U12" s="24"/>
     </row>
-    <row r="13">
+    <row r="13" ht="6.0" customHeight="true">
       <c r="A13" s="0"/>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14" ht="102.56" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="20" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
       <c r="T14" s="20"/>
       <c r="U14" s="20"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="458.98" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="23" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
       </c>
       <c r="U15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="458.98" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="23" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
       <c r="T16" s="23"/>
       <c r="U16" s="24"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="458.98" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="23"/>
       <c r="C17" s="24"/>
@@ -14723,7 +14723,7 @@
       <c r="T17" s="23"/>
       <c r="U17" s="24"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="458.98" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="23" t="inlineStr">
         <is>
@@ -14790,10 +14790,10 @@
       </c>
       <c r="U18" s="24"/>
     </row>
-    <row r="19">
+    <row r="19" ht="6.0" customHeight="true">
       <c r="A19" s="0"/>
     </row>
-    <row r="20" ht="60" customHeight="1">
+    <row r="20" ht="102.56" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="20" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
       <c r="T20" s="20"/>
       <c r="U20" s="20"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="458.98" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="23" t="inlineStr">
         <is>
@@ -14897,7 +14897,7 @@
       </c>
       <c r="U21" s="24"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="458.98" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="23" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
       <c r="T22" s="23"/>
       <c r="U22" s="24"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="458.98" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="23" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
       </c>
       <c r="U23" s="24"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="458.98" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="23" t="inlineStr">
         <is>
@@ -15056,10 +15056,10 @@
       </c>
       <c r="U24" s="24"/>
     </row>
-    <row r="25">
+    <row r="25" ht="6.0" customHeight="true">
       <c r="A25" s="0"/>
     </row>
-    <row r="26" ht="60" customHeight="1">
+    <row r="26" ht="102.56" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="20" t="inlineStr">
         <is>
@@ -15086,7 +15086,7 @@
       <c r="T26" s="20"/>
       <c r="U26" s="20"/>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="458.98" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="23" t="inlineStr">
         <is>
@@ -15163,7 +15163,7 @@
       </c>
       <c r="U27" s="22"/>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="458.98" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="23" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
       <c r="T28" s="23"/>
       <c r="U28" s="24"/>
     </row>
-    <row r="29" ht="56" customHeight="1">
+    <row r="29" ht="458.98" customHeight="true">
       <c r="A29" s="0"/>
       <c r="B29" s="23" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
       <c r="T29" s="23"/>
       <c r="U29" s="24"/>
     </row>
-    <row r="30" ht="56" customHeight="1">
+    <row r="30" ht="458.98" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="23" t="inlineStr">
         <is>
@@ -15390,10 +15390,10 @@
       </c>
       <c r="U30" s="24"/>
     </row>
-    <row r="31">
+    <row r="31" ht="6.0" customHeight="true">
       <c r="A31" s="0"/>
     </row>
-    <row r="32" ht="60" customHeight="1">
+    <row r="32" ht="102.56" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="20" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
       <c r="T32" s="20"/>
       <c r="U32" s="20"/>
     </row>
-    <row r="33" ht="56" customHeight="1">
+    <row r="33" ht="458.98" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
       </c>
       <c r="U33" s="24"/>
     </row>
-    <row r="34" ht="56" customHeight="1">
+    <row r="34" ht="458.98" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="23" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
       </c>
       <c r="U34" s="24"/>
     </row>
-    <row r="35" ht="56" customHeight="1">
+    <row r="35" ht="458.98" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="23" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
       </c>
       <c r="U35" s="22"/>
     </row>
-    <row r="36" ht="56" customHeight="1">
+    <row r="36" ht="458.98" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="23" t="inlineStr">
         <is>
@@ -15740,10 +15740,10 @@
       </c>
       <c r="U36" s="24"/>
     </row>
-    <row r="37">
+    <row r="37" ht="6.0" customHeight="true">
       <c r="A37" s="0"/>
     </row>
-    <row r="38" ht="60" customHeight="1">
+    <row r="38" ht="102.56" customHeight="true">
       <c r="A38" s="0"/>
       <c r="B38" s="20" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
       <c r="T38" s="20"/>
       <c r="U38" s="20"/>
     </row>
-    <row r="39" ht="56" customHeight="1">
+    <row r="39" ht="458.98" customHeight="true">
       <c r="A39" s="0"/>
       <c r="B39" s="23" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="U39" s="24"/>
     </row>
-    <row r="40" ht="56" customHeight="1">
+    <row r="40" ht="458.98" customHeight="true">
       <c r="A40" s="0"/>
       <c r="B40" s="23"/>
       <c r="C40" s="24"/>
@@ -15920,7 +15920,7 @@
       </c>
       <c r="U40" s="24"/>
     </row>
-    <row r="41" ht="56" customHeight="1">
+    <row r="41" ht="458.98" customHeight="true">
       <c r="A41" s="0"/>
       <c r="B41" s="23"/>
       <c r="C41" s="24"/>
@@ -15992,7 +15992,7 @@
       </c>
       <c r="U41" s="22"/>
     </row>
-    <row r="42" ht="56" customHeight="1">
+    <row r="42" ht="458.98" customHeight="true">
       <c r="A42" s="0"/>
       <c r="B42" s="23" t="inlineStr">
         <is>
@@ -16073,10 +16073,10 @@
       </c>
       <c r="U42" s="24"/>
     </row>
-    <row r="43">
+    <row r="43" ht="6.0" customHeight="true">
       <c r="A43" s="0"/>
     </row>
-    <row r="44" ht="60" customHeight="1">
+    <row r="44" ht="102.56" customHeight="true">
       <c r="A44" s="0"/>
       <c r="B44" s="20" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
       <c r="T44" s="20"/>
       <c r="U44" s="20"/>
     </row>
-    <row r="45" ht="56" customHeight="1">
+    <row r="45" ht="458.98" customHeight="true">
       <c r="A45" s="0"/>
       <c r="B45" s="23" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
       </c>
       <c r="U45" s="24"/>
     </row>
-    <row r="46" ht="56" customHeight="1">
+    <row r="46" ht="458.98" customHeight="true">
       <c r="A46" s="0"/>
       <c r="B46" s="23"/>
       <c r="C46" s="24"/>
@@ -16243,7 +16243,7 @@
       </c>
       <c r="U46" s="22"/>
     </row>
-    <row r="47" ht="56" customHeight="1">
+    <row r="47" ht="458.98" customHeight="true">
       <c r="A47" s="0"/>
       <c r="B47" s="23"/>
       <c r="C47" s="24"/>
@@ -16302,7 +16302,7 @@
       <c r="T47" s="23"/>
       <c r="U47" s="24"/>
     </row>
-    <row r="48" ht="56" customHeight="1">
+    <row r="48" ht="458.98" customHeight="true">
       <c r="A48" s="0"/>
       <c r="B48" s="23" t="inlineStr">
         <is>
@@ -16379,10 +16379,10 @@
       </c>
       <c r="U48" s="24"/>
     </row>
-    <row r="49">
+    <row r="49" ht="6.0" customHeight="true">
       <c r="A49" s="0"/>
     </row>
-    <row r="50" ht="60" customHeight="1">
+    <row r="50" ht="102.56" customHeight="true">
       <c r="A50" s="0"/>
       <c r="B50" s="20" t="inlineStr">
         <is>
@@ -16409,7 +16409,7 @@
       <c r="T50" s="20"/>
       <c r="U50" s="20"/>
     </row>
-    <row r="51" ht="56" customHeight="1">
+    <row r="51" ht="458.98" customHeight="true">
       <c r="A51" s="0"/>
       <c r="B51" s="21" t="inlineStr">
         <is>
@@ -16486,7 +16486,7 @@
       </c>
       <c r="U51" s="24"/>
     </row>
-    <row r="52" ht="56" customHeight="1">
+    <row r="52" ht="458.98" customHeight="true">
       <c r="A52" s="0"/>
       <c r="B52" s="23"/>
       <c r="C52" s="24"/>
@@ -16521,7 +16521,7 @@
       <c r="T52" s="23"/>
       <c r="U52" s="24"/>
     </row>
-    <row r="53" ht="56" customHeight="1">
+    <row r="53" ht="458.98" customHeight="true">
       <c r="A53" s="0"/>
       <c r="B53" s="23"/>
       <c r="C53" s="24"/>
@@ -16562,7 +16562,7 @@
       <c r="T53" s="23"/>
       <c r="U53" s="24"/>
     </row>
-    <row r="54" ht="56" customHeight="1">
+    <row r="54" ht="458.98" customHeight="true">
       <c r="A54" s="0"/>
       <c r="B54" s="23" t="inlineStr">
         <is>
@@ -16637,10 +16637,10 @@
       </c>
       <c r="U54" s="24"/>
     </row>
-    <row r="55">
+    <row r="55" ht="6.0" customHeight="true">
       <c r="A55" s="0"/>
     </row>
-    <row r="56" ht="60" customHeight="1">
+    <row r="56" ht="102.56" customHeight="true">
       <c r="A56" s="0"/>
       <c r="B56" s="20" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
       <c r="T56" s="20"/>
       <c r="U56" s="20"/>
     </row>
-    <row r="57" ht="56" customHeight="1">
+    <row r="57" ht="458.98" customHeight="true">
       <c r="A57" s="0"/>
       <c r="B57" s="23" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="U57" s="24"/>
     </row>
-    <row r="58" ht="56" customHeight="1">
+    <row r="58" ht="458.98" customHeight="true">
       <c r="A58" s="0"/>
       <c r="B58" s="23" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
       <c r="T58" s="23"/>
       <c r="U58" s="24"/>
     </row>
-    <row r="59" ht="56" customHeight="1">
+    <row r="59" ht="458.98" customHeight="true">
       <c r="A59" s="0"/>
       <c r="B59" s="23" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
       <c r="T59" s="23"/>
       <c r="U59" s="24"/>
     </row>
-    <row r="60" ht="56" customHeight="1">
+    <row r="60" ht="458.98" customHeight="true">
       <c r="A60" s="0"/>
       <c r="B60" s="23" t="inlineStr">
         <is>
@@ -16963,10 +16963,10 @@
       </c>
       <c r="U60" s="24"/>
     </row>
-    <row r="61">
+    <row r="61" ht="6.0" customHeight="true">
       <c r="A61" s="0"/>
     </row>
-    <row r="62" ht="60" customHeight="1">
+    <row r="62" ht="102.56" customHeight="true">
       <c r="A62" s="0"/>
       <c r="B62" s="20" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
       <c r="T62" s="20"/>
       <c r="U62" s="20"/>
     </row>
-    <row r="63" ht="56" customHeight="1">
+    <row r="63" ht="458.98" customHeight="true">
       <c r="A63" s="0"/>
       <c r="B63" s="23" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
       </c>
       <c r="U63" s="24"/>
     </row>
-    <row r="64" ht="56" customHeight="1">
+    <row r="64" ht="458.98" customHeight="true">
       <c r="A64" s="0"/>
       <c r="B64" s="23"/>
       <c r="C64" s="24"/>
@@ -17124,7 +17124,7 @@
       </c>
       <c r="U64" s="24"/>
     </row>
-    <row r="65" ht="56" customHeight="1">
+    <row r="65" ht="458.98" customHeight="true">
       <c r="A65" s="0"/>
       <c r="B65" s="23"/>
       <c r="C65" s="24"/>
@@ -17183,7 +17183,7 @@
       </c>
       <c r="U65" s="24"/>
     </row>
-    <row r="66" ht="56" customHeight="1">
+    <row r="66" ht="458.98" customHeight="true">
       <c r="A66" s="0"/>
       <c r="B66" s="23" t="inlineStr">
         <is>
@@ -17260,10 +17260,10 @@
       </c>
       <c r="U66" s="24"/>
     </row>
-    <row r="67">
+    <row r="67" ht="6.0" customHeight="true">
       <c r="A67" s="0"/>
     </row>
-    <row r="68" ht="60" customHeight="1">
+    <row r="68" ht="102.56" customHeight="true">
       <c r="A68" s="0"/>
       <c r="B68" s="20" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
       <c r="T68" s="20"/>
       <c r="U68" s="20"/>
     </row>
-    <row r="69" ht="56" customHeight="1">
+    <row r="69" ht="458.98" customHeight="true">
       <c r="A69" s="0"/>
       <c r="B69" s="23" t="inlineStr">
         <is>
@@ -17373,7 +17373,7 @@
       </c>
       <c r="U69" s="24"/>
     </row>
-    <row r="70" ht="56" customHeight="1">
+    <row r="70" ht="458.98" customHeight="true">
       <c r="A70" s="0"/>
       <c r="B70" s="23" t="inlineStr">
         <is>
@@ -17444,7 +17444,7 @@
       </c>
       <c r="U70" s="24"/>
     </row>
-    <row r="71" ht="56" customHeight="1">
+    <row r="71" ht="458.98" customHeight="true">
       <c r="A71" s="0"/>
       <c r="B71" s="23" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
       </c>
       <c r="U71" s="24"/>
     </row>
-    <row r="72" ht="56" customHeight="1">
+    <row r="72" ht="458.98" customHeight="true">
       <c r="A72" s="0"/>
       <c r="B72" s="23" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="39"/>
   <rowBreaks count="11" manualBreakCount="11">
     <brk id="6" max="16383" man="1"/>
     <brk id="12" max="16383" man="1"/>
